--- a/artfynd/A 56883-2022 artfynd.xlsx
+++ b/artfynd/A 56883-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 56883-2022 artfynd.xlsx
+++ b/artfynd/A 56883-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -789,6 +789,1046 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>120496540</v>
+      </c>
+      <c r="B3" t="n">
+        <v>79624</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>512804</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7129114</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>120497662</v>
+      </c>
+      <c r="B4" t="n">
+        <v>78187</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>353</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>512632</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7129005</v>
+      </c>
+      <c r="S4" t="n">
+        <v>15</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>120495814</v>
+      </c>
+      <c r="B5" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>512928</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7129053</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>120496293</v>
+      </c>
+      <c r="B6" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>512862</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7129162</v>
+      </c>
+      <c r="S6" t="n">
+        <v>15</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>120497415</v>
+      </c>
+      <c r="B7" t="n">
+        <v>91277</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>67</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Sprickporing</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Diplomitoporus crustulinus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Bres.) Domański</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>512742</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7129118</v>
+      </c>
+      <c r="S7" t="n">
+        <v>15</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>120497656</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79160</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>512632</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7129002</v>
+      </c>
+      <c r="S8" t="n">
+        <v>15</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>120496212</v>
+      </c>
+      <c r="B9" t="n">
+        <v>90576</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>512903</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7129098</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>120495864</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>512926</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7129048</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>120496418</v>
+      </c>
+      <c r="B11" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>512828</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7129137</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>120496882</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Grevetjärnen, Grevetjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>512822</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7129085</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 56883-2022 artfynd.xlsx
+++ b/artfynd/A 56883-2022 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120496540</v>
+        <v>120497662</v>
       </c>
       <c r="B3" t="n">
-        <v>79624</v>
+        <v>78187</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,21 +808,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,13 +832,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>512804</v>
+        <v>512632</v>
       </c>
       <c r="R3" t="n">
-        <v>7129114</v>
+        <v>7129005</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -894,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120497662</v>
+        <v>120496540</v>
       </c>
       <c r="B4" t="n">
-        <v>78187</v>
+        <v>79624</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -910,21 +910,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,13 +934,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>512632</v>
+        <v>512804</v>
       </c>
       <c r="R4" t="n">
-        <v>7129005</v>
+        <v>7129114</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 56883-2022 artfynd.xlsx
+++ b/artfynd/A 56883-2022 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120497662</v>
+        <v>120495814</v>
       </c>
       <c r="B3" t="n">
-        <v>78187</v>
+        <v>78542</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,21 +808,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,13 +832,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>512632</v>
+        <v>512928</v>
       </c>
       <c r="R3" t="n">
-        <v>7129005</v>
+        <v>7129053</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -894,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120496540</v>
+        <v>120495864</v>
       </c>
       <c r="B4" t="n">
-        <v>79624</v>
+        <v>57320</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -910,34 +910,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Grevetjärnen, Grevetjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>512804</v>
+        <v>512926</v>
       </c>
       <c r="R4" t="n">
-        <v>7129114</v>
+        <v>7129048</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -970,6 +975,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120495814</v>
+        <v>120497662</v>
       </c>
       <c r="B5" t="n">
-        <v>78542</v>
+        <v>78187</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,21 +1022,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,13 +1046,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>512928</v>
+        <v>512632</v>
       </c>
       <c r="R5" t="n">
-        <v>7129053</v>
+        <v>7129005</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1098,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120496293</v>
+        <v>120496540</v>
       </c>
       <c r="B6" t="n">
-        <v>78542</v>
+        <v>79624</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1114,21 +1124,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,13 +1148,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>512862</v>
+        <v>512804</v>
       </c>
       <c r="R6" t="n">
-        <v>7129162</v>
+        <v>7129114</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1200,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120497415</v>
+        <v>120496212</v>
       </c>
       <c r="B7" t="n">
-        <v>91277</v>
+        <v>90576</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1212,25 +1222,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>67</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,13 +1250,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>512742</v>
+        <v>512903</v>
       </c>
       <c r="R7" t="n">
-        <v>7129118</v>
+        <v>7129098</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1302,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120497656</v>
+        <v>120496293</v>
       </c>
       <c r="B8" t="n">
-        <v>79160</v>
+        <v>78542</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1318,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>512632</v>
+        <v>512862</v>
       </c>
       <c r="R8" t="n">
-        <v>7129002</v>
+        <v>7129162</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1404,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120496212</v>
+        <v>120497415</v>
       </c>
       <c r="B9" t="n">
-        <v>90576</v>
+        <v>91277</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1416,25 +1426,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1108</v>
+        <v>67</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1444,13 +1454,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>512903</v>
+        <v>512742</v>
       </c>
       <c r="R9" t="n">
-        <v>7129098</v>
+        <v>7129118</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1506,10 +1516,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120495864</v>
+        <v>120496418</v>
       </c>
       <c r="B10" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1522,39 +1532,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Grevetjärnen, Grevetjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>512926</v>
+        <v>512828</v>
       </c>
       <c r="R10" t="n">
-        <v>7129048</v>
+        <v>7129137</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1587,11 +1592,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-10-19</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1618,10 +1618,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120496418</v>
+        <v>120496882</v>
       </c>
       <c r="B11" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1634,34 +1634,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Grevetjärnen, Grevetjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>512828</v>
+        <v>512822</v>
       </c>
       <c r="R11" t="n">
-        <v>7129137</v>
+        <v>7129085</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1694,6 +1699,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1720,10 +1730,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120496882</v>
+        <v>120497656</v>
       </c>
       <c r="B12" t="n">
-        <v>57320</v>
+        <v>79160</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1736,42 +1746,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Grevetjärnen, Grevetjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>512822</v>
+        <v>512632</v>
       </c>
       <c r="R12" t="n">
-        <v>7129085</v>
+        <v>7129002</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1801,11 +1806,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-10-19</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 56883-2022 artfynd.xlsx
+++ b/artfynd/A 56883-2022 artfynd.xlsx
@@ -894,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120495864</v>
+        <v>120496212</v>
       </c>
       <c r="B4" t="n">
-        <v>57320</v>
+        <v>90576</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -910,39 +910,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Grevetjärnen, Grevetjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>512926</v>
+        <v>512903</v>
       </c>
       <c r="R4" t="n">
-        <v>7129048</v>
+        <v>7129098</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -975,11 +970,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-10-19</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120497662</v>
+        <v>120496293</v>
       </c>
       <c r="B5" t="n">
-        <v>78187</v>
+        <v>78542</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1022,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1046,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>512632</v>
+        <v>512862</v>
       </c>
       <c r="R5" t="n">
-        <v>7129005</v>
+        <v>7129162</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1108,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120496540</v>
+        <v>120497656</v>
       </c>
       <c r="B6" t="n">
-        <v>79624</v>
+        <v>79160</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1124,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1148,13 +1138,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>512804</v>
+        <v>512632</v>
       </c>
       <c r="R6" t="n">
-        <v>7129114</v>
+        <v>7129002</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1210,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120496212</v>
+        <v>120496882</v>
       </c>
       <c r="B7" t="n">
-        <v>90576</v>
+        <v>57320</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,34 +1216,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Grevetjärnen, Grevetjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>512903</v>
+        <v>512822</v>
       </c>
       <c r="R7" t="n">
-        <v>7129098</v>
+        <v>7129085</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1286,6 +1281,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120496293</v>
+        <v>120497415</v>
       </c>
       <c r="B8" t="n">
-        <v>78542</v>
+        <v>91277</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1324,25 +1324,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>67</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>512862</v>
+        <v>512742</v>
       </c>
       <c r="R8" t="n">
-        <v>7129162</v>
+        <v>7129118</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1414,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120497415</v>
+        <v>120496418</v>
       </c>
       <c r="B9" t="n">
-        <v>91277</v>
+        <v>78542</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1426,25 +1426,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>67</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1454,13 +1454,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>512742</v>
+        <v>512828</v>
       </c>
       <c r="R9" t="n">
-        <v>7129118</v>
+        <v>7129137</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1516,10 +1516,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120496418</v>
+        <v>120495864</v>
       </c>
       <c r="B10" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1532,34 +1532,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Grevetjärnen, Grevetjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>512828</v>
+        <v>512926</v>
       </c>
       <c r="R10" t="n">
-        <v>7129137</v>
+        <v>7129048</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1592,6 +1597,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1618,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120496882</v>
+        <v>120497662</v>
       </c>
       <c r="B11" t="n">
-        <v>57320</v>
+        <v>78187</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1634,42 +1644,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Grevetjärnen, Grevetjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>512822</v>
+        <v>512632</v>
       </c>
       <c r="R11" t="n">
-        <v>7129085</v>
+        <v>7129005</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1699,11 +1704,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-10-19</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1730,10 +1730,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120497656</v>
+        <v>120496540</v>
       </c>
       <c r="B12" t="n">
-        <v>79160</v>
+        <v>79624</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1746,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1770,13 +1770,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>512632</v>
+        <v>512804</v>
       </c>
       <c r="R12" t="n">
-        <v>7129002</v>
+        <v>7129114</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
